--- a/SistemaDinamicoDados/AmostrasFiltradas/KrigingVsg/content/KrigingMetrics.xlsx
+++ b/SistemaDinamicoDados/AmostrasFiltradas/KrigingVsg/content/KrigingMetrics.xlsx
@@ -477,28 +477,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0.9999999999989769</v>
       </c>
       <c r="B2" t="n">
-        <v>1.132827206569714e-25</v>
+        <v>2.468164681952484e-13</v>
       </c>
       <c r="C2" t="n">
-        <v>2.342805554355148e-11</v>
+        <v>1.908094124660819e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>3.365749851919649e-13</v>
+        <v>4.968062682729038e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5409407984114138</v>
+        <v>0.9207490962623099</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04675744522565498</v>
+        <v>0.01307146510359875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3201856473109275</v>
+        <v>0.4151418497286916</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2162346994024201</v>
+        <v>0.11433050819269</v>
       </c>
     </row>
   </sheetData>
@@ -562,25 +562,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.981824912773589e-24</v>
+        <v>8.177136279131521e-25</v>
       </c>
       <c r="C2" t="n">
-        <v>1.162128662129263e-10</v>
+        <v>4.002606902549193e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.726796141058229e-12</v>
+        <v>9.042751947903647e-13</v>
       </c>
       <c r="E2" t="n">
-        <v>-11.59385082649155</v>
+        <v>0.9473556707933627</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3821407615443836</v>
+        <v>0.008683036781568719</v>
       </c>
       <c r="G2" t="n">
-        <v>1.00449277553823</v>
+        <v>0.3062579516314428</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6181753485414827</v>
+        <v>0.09318281376717875</v>
       </c>
     </row>
   </sheetData>
@@ -644,25 +644,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1.82863216609794e-24</v>
+        <v>2.108853076289439e-24</v>
       </c>
       <c r="C2" t="n">
-        <v>1.183069903234108e-10</v>
+        <v>5.441333042567264e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.352269265382431e-12</v>
+        <v>1.452189063548352e-12</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.32790258238599</v>
+        <v>0.9253834007755422</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5257881786935995</v>
+        <v>0.01230709338205135</v>
       </c>
       <c r="G2" t="n">
-        <v>1.197639999988752</v>
+        <v>0.3716790346497804</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7251125282972288</v>
+        <v>0.1109373398908201</v>
       </c>
     </row>
   </sheetData>
@@ -726,25 +726,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1.240930890471205e-25</v>
+        <v>1.632402400914816e-27</v>
       </c>
       <c r="C2" t="n">
-        <v>1.220472847568245e-11</v>
+        <v>2.673284631375272e-13</v>
       </c>
       <c r="D2" t="n">
-        <v>3.522684900003412e-13</v>
+        <v>4.040299989994327e-14</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.3483569433669</v>
+        <v>0.9217261541684055</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5264088343762685</v>
+        <v>0.01291031137889176</v>
       </c>
       <c r="G2" t="n">
-        <v>1.207291986396632</v>
+        <v>0.4203843007488542</v>
       </c>
       <c r="H2" t="n">
-        <v>0.725540374049762</v>
+        <v>0.1136235511630039</v>
       </c>
     </row>
   </sheetData>
@@ -808,25 +808,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.038661019646193e-27</v>
+        <v>1.412619891032524e-26</v>
       </c>
       <c r="C2" t="n">
-        <v>6.56401129592957e-13</v>
+        <v>3.358258599698746e-12</v>
       </c>
       <c r="D2" t="n">
-        <v>8.389672830120489e-14</v>
+        <v>1.188536869866696e-13</v>
       </c>
       <c r="E2" t="n">
-        <v>-10.45627119680756</v>
+        <v>-0.05234852166906534</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3476226818883678</v>
+        <v>0.1735719888236301</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9709458212264445</v>
+        <v>3.303299763415427</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5895953543646419</v>
+        <v>0.4166197172765952</v>
       </c>
     </row>
   </sheetData>
@@ -890,25 +890,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.39687685260468e-25</v>
+        <v>1.235144176913795e-24</v>
       </c>
       <c r="C2" t="n">
-        <v>4.139543496660503e-11</v>
+        <v>6.42191183223389e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>6.630895001886759e-13</v>
+        <v>1.11137040491179e-12</v>
       </c>
       <c r="E2" t="n">
-        <v>-18.02208585051229</v>
+        <v>0.9294417108543372</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5771955276607379</v>
+        <v>0.01163772488184932</v>
       </c>
       <c r="G2" t="n">
-        <v>1.271122173868237</v>
+        <v>0.4311357069691023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7597338531753984</v>
+        <v>0.1078782873512985</v>
       </c>
     </row>
   </sheetData>
